--- a/Diego Ambiente e Performance.xlsx
+++ b/Diego Ambiente e Performance.xlsx
@@ -1,24 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\daf21\source\repos\CutoverPlanner\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75C1E80E-9ABE-4067-AAF4-51621BFF1253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1409CB6-C2AC-4F07-8554-AD04367646A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22395" yWindow="1890" windowWidth="20580" windowHeight="12645" tabRatio="540" xr2:uid="{C97315FB-AC97-4FBC-B50C-226D58C7FA99}"/>
+    <workbookView xWindow="-5715" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="540" xr2:uid="{C97315FB-AC97-4FBC-B50C-226D58C7FA99}"/>
   </bookViews>
   <sheets>
     <sheet name="Plano Cutover Consolidado" sheetId="1" r:id="rId1"/>
-    <sheet name="Endpoints" sheetId="3" r:id="rId2"/>
-    <sheet name="Area Executora" sheetId="2" r:id="rId3"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId4"/>
+    <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Plano Cutover Consolidado'!$A$1:$P$97</definedName>
@@ -45,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="802" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="158">
   <si>
     <t>Caminho Crítico</t>
   </si>
@@ -519,132 +517,6 @@
   </si>
   <si>
     <t>Charles Correa/Mailton Fernandes</t>
-  </si>
-  <si>
-    <t>CUTOVER ADMS - Integrações</t>
-  </si>
-  <si>
-    <t>Sistemas</t>
-  </si>
-  <si>
-    <t>Tipo Integração</t>
-  </si>
-  <si>
-    <t>Barramento</t>
-  </si>
-  <si>
-    <t>Integração</t>
-  </si>
-  <si>
-    <t>Endpoint (URL)</t>
-  </si>
-  <si>
-    <t>ADMS</t>
-  </si>
-  <si>
-    <t>SIGOD</t>
-  </si>
-  <si>
-    <t>WFM</t>
-  </si>
-  <si>
-    <t>SIATT</t>
-  </si>
-  <si>
-    <t>Gerência</t>
-  </si>
-  <si>
-    <t>Nome da área executora</t>
-  </si>
-  <si>
-    <t>Torre</t>
-  </si>
-  <si>
-    <t>Responsável</t>
-  </si>
-  <si>
-    <t>Executor</t>
-  </si>
-  <si>
-    <t>GOTIC</t>
-  </si>
-  <si>
-    <t>Andre Lomba/Eduardo Celso</t>
-  </si>
-  <si>
-    <t>INFRA SEGURANÇA FIREWALL</t>
-  </si>
-  <si>
-    <t>Marcos Anunciacao</t>
-  </si>
-  <si>
-    <t>Rafael de Oliveira Gama/Samuel Lanes</t>
-  </si>
-  <si>
-    <t>INFRA CITRIX OT</t>
-  </si>
-  <si>
-    <t>Thiago de Farias</t>
-  </si>
-  <si>
-    <t>INFRA CITRIX IT</t>
-  </si>
-  <si>
-    <t>Manoel Ptak/Ramon de Oliveira/Gilmar de Alcantara</t>
-  </si>
-  <si>
-    <t>INFRA IDENTIDADE AD</t>
-  </si>
-  <si>
-    <t>Rafael Mochinsky / Carlos Weber</t>
-  </si>
-  <si>
-    <t>Rogerio dos Santos Lima</t>
-  </si>
-  <si>
-    <t>Cristiano Paschoalim/Ghulite</t>
-  </si>
-  <si>
-    <t>INFRA SERVIDORES</t>
-  </si>
-  <si>
-    <t>Matheus Ferreira/Luciano Gama</t>
-  </si>
-  <si>
-    <t>INFRA CLOUD</t>
-  </si>
-  <si>
-    <t>Weslei Louzado/Flavio Procaci/Anderson Sebastiao</t>
-  </si>
-  <si>
-    <t>GEAP</t>
-  </si>
-  <si>
-    <t>SISTEMAS TERCEIROS</t>
-  </si>
-  <si>
-    <t>Gilmar Pedretti Junior</t>
-  </si>
-  <si>
-    <t>Bruno César/Caroline Soares/Aniello</t>
-  </si>
-  <si>
-    <t>CANAIS CONVENCIONAIS</t>
-  </si>
-  <si>
-    <t>CANAIS DIGITAIS</t>
-  </si>
-  <si>
-    <t>COBRANÇA</t>
-  </si>
-  <si>
-    <t>FATURAMENTO</t>
-  </si>
-  <si>
-    <t>OPERAÇÃO DESPACHO</t>
-  </si>
-  <si>
-    <t>OPERAÇÃO MANUTENÇÃO</t>
   </si>
 </sst>
 </file>
@@ -655,7 +527,7 @@
     <numFmt numFmtId="164" formatCode="m/d/yy;@"/>
     <numFmt numFmtId="165" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -740,12 +612,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="22"/>
       <color theme="1" tint="0.34998626667073579"/>
@@ -753,24 +619,8 @@
       <family val="2"/>
       <scheme val="major"/>
     </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Aptos Display"/>
-      <family val="2"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -813,14 +663,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="1" tint="0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -848,23 +692,8 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="hair">
-        <color auto="1"/>
-      </left>
-      <right style="hair">
-        <color auto="1"/>
-      </right>
-      <top style="hair">
-        <color auto="1"/>
-      </top>
-      <bottom style="hair">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="7">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyFill="0">
@@ -876,10 +705,9 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="2" applyFill="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -947,30 +775,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="6" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="6"/>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="2" xfId="3" applyFont="1" applyFill="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="7">
+  <cellStyles count="6">
     <cellStyle name="Date" xfId="4" xr:uid="{FFECA42C-8B6E-436A-8354-3C866A472306}"/>
-    <cellStyle name="Hiperlink" xfId="6" builtinId="8"/>
     <cellStyle name="Name" xfId="3" xr:uid="{BCD8EA8B-C631-4855-9721-880C6CE327F4}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Task" xfId="2" xr:uid="{1B4A94E2-AF59-42AE-B5F2-055616BB15B5}"/>
@@ -1277,6 +1087,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="PLANO CUTOVER"/>
@@ -1771,7 +1582,7 @@
       <c r="J2" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K2" s="31"/>
+      <c r="K2" s="23"/>
       <c r="L2" s="16">
         <v>46064</v>
       </c>
@@ -1812,7 +1623,7 @@
       <c r="J3" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K3" s="31"/>
+      <c r="K3" s="23"/>
       <c r="L3" s="16">
         <v>46064</v>
       </c>
@@ -1853,7 +1664,7 @@
       <c r="J4" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K4" s="31"/>
+      <c r="K4" s="23"/>
       <c r="L4" s="16">
         <v>46064</v>
       </c>
@@ -1894,7 +1705,7 @@
       <c r="J5" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K5" s="31"/>
+      <c r="K5" s="23"/>
       <c r="L5" s="16">
         <v>46064</v>
       </c>
@@ -1935,7 +1746,7 @@
       <c r="J6" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K6" s="31"/>
+      <c r="K6" s="23"/>
       <c r="L6" s="16">
         <v>46064</v>
       </c>
@@ -1976,7 +1787,7 @@
       <c r="J7" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K7" s="31"/>
+      <c r="K7" s="23"/>
       <c r="L7" s="16">
         <v>46064</v>
       </c>
@@ -2017,7 +1828,7 @@
       <c r="J8" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K8" s="31"/>
+      <c r="K8" s="23"/>
       <c r="L8" s="16">
         <v>46064</v>
       </c>
@@ -2058,7 +1869,7 @@
       <c r="J9" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="31"/>
+      <c r="K9" s="23"/>
       <c r="L9" s="16">
         <v>46064</v>
       </c>
@@ -2099,7 +1910,7 @@
       <c r="J10" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="31"/>
+      <c r="K10" s="23"/>
       <c r="L10" s="16">
         <v>46064</v>
       </c>
@@ -2140,7 +1951,7 @@
       <c r="J11" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="31"/>
+      <c r="K11" s="23"/>
       <c r="L11" s="16">
         <v>46064</v>
       </c>
@@ -2181,7 +1992,7 @@
       <c r="J12" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K12" s="31"/>
+      <c r="K12" s="23"/>
       <c r="L12" s="16">
         <v>46064</v>
       </c>
@@ -2222,7 +2033,7 @@
       <c r="J13" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K13" s="31"/>
+      <c r="K13" s="23"/>
       <c r="L13" s="16">
         <v>46064</v>
       </c>
@@ -2263,7 +2074,7 @@
       <c r="J14" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K14" s="31"/>
+      <c r="K14" s="23"/>
       <c r="L14" s="16">
         <v>46064</v>
       </c>
@@ -2304,7 +2115,7 @@
       <c r="J15" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K15" s="31"/>
+      <c r="K15" s="23"/>
       <c r="L15" s="16">
         <v>46063</v>
       </c>
@@ -2348,7 +2159,7 @@
       <c r="J16" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K16" s="31"/>
+      <c r="K16" s="23"/>
       <c r="L16" s="16">
         <v>46063</v>
       </c>
@@ -2394,7 +2205,7 @@
       <c r="J17" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K17" s="31"/>
+      <c r="K17" s="23"/>
       <c r="L17" s="16">
         <v>46064</v>
       </c>
@@ -2435,7 +2246,7 @@
       <c r="J18" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K18" s="31"/>
+      <c r="K18" s="23"/>
       <c r="L18" s="16">
         <v>46063</v>
       </c>
@@ -2479,7 +2290,7 @@
       <c r="J19" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K19" s="31"/>
+      <c r="K19" s="23"/>
       <c r="L19" s="16">
         <v>46063</v>
       </c>
@@ -2525,7 +2336,7 @@
       <c r="J20" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K20" s="31"/>
+      <c r="K20" s="23"/>
       <c r="L20" s="16">
         <v>46064</v>
       </c>
@@ -2566,7 +2377,7 @@
       <c r="J21" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K21" s="31"/>
+      <c r="K21" s="23"/>
       <c r="L21" s="16">
         <v>46063</v>
       </c>
@@ -2607,7 +2418,7 @@
       <c r="J22" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K22" s="31"/>
+      <c r="K22" s="23"/>
       <c r="L22" s="16">
         <v>46063</v>
       </c>
@@ -2648,7 +2459,7 @@
       <c r="J23" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K23" s="31"/>
+      <c r="K23" s="23"/>
       <c r="L23" s="16">
         <v>46063</v>
       </c>
@@ -2691,7 +2502,7 @@
       <c r="J24" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K24" s="31"/>
+      <c r="K24" s="23"/>
       <c r="L24" s="16">
         <v>46063</v>
       </c>
@@ -2732,7 +2543,7 @@
       <c r="J25" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K25" s="31"/>
+      <c r="K25" s="23"/>
       <c r="L25" s="16">
         <v>46063</v>
       </c>
@@ -2773,7 +2584,7 @@
       <c r="J26" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K26" s="31"/>
+      <c r="K26" s="23"/>
       <c r="L26" s="16">
         <v>46064</v>
       </c>
@@ -2817,7 +2628,7 @@
       <c r="J27" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K27" s="31"/>
+      <c r="K27" s="23"/>
       <c r="L27" s="16">
         <v>46064</v>
       </c>
@@ -2861,7 +2672,7 @@
       <c r="J28" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K28" s="31"/>
+      <c r="K28" s="23"/>
       <c r="L28" s="16">
         <v>46064</v>
       </c>
@@ -2905,7 +2716,7 @@
       <c r="J29" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K29" s="31"/>
+      <c r="K29" s="23"/>
       <c r="L29" s="16">
         <v>46065</v>
       </c>
@@ -2946,7 +2757,7 @@
       <c r="J30" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K30" s="31"/>
+      <c r="K30" s="23"/>
       <c r="L30" s="16">
         <v>46064</v>
       </c>
@@ -2987,7 +2798,7 @@
       <c r="J31" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K31" s="31"/>
+      <c r="K31" s="23"/>
       <c r="L31" s="16">
         <v>46064</v>
       </c>
@@ -3028,7 +2839,7 @@
       <c r="J32" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K32" s="31"/>
+      <c r="K32" s="23"/>
       <c r="L32" s="16">
         <v>46064</v>
       </c>
@@ -3071,7 +2882,7 @@
       <c r="J33" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K33" s="31"/>
+      <c r="K33" s="23"/>
       <c r="L33" s="16">
         <v>46064</v>
       </c>
@@ -3112,7 +2923,7 @@
       <c r="J34" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K34" s="31"/>
+      <c r="K34" s="23"/>
       <c r="L34" s="16">
         <v>46064</v>
       </c>
@@ -3153,7 +2964,7 @@
       <c r="J35" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K35" s="31"/>
+      <c r="K35" s="23"/>
       <c r="L35" s="16">
         <v>46064</v>
       </c>
@@ -3197,7 +3008,7 @@
       <c r="J36" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K36" s="31"/>
+      <c r="K36" s="23"/>
       <c r="L36" s="16">
         <v>46064</v>
       </c>
@@ -3241,7 +3052,7 @@
       <c r="J37" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K37" s="31"/>
+      <c r="K37" s="23"/>
       <c r="L37" s="16">
         <v>46065</v>
       </c>
@@ -3285,7 +3096,7 @@
       <c r="J38" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K38" s="31"/>
+      <c r="K38" s="23"/>
       <c r="L38" s="16">
         <v>46065</v>
       </c>
@@ -3329,7 +3140,7 @@
       <c r="J39" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K39" s="31"/>
+      <c r="K39" s="23"/>
       <c r="L39" s="16">
         <v>46065</v>
       </c>
@@ -3375,7 +3186,7 @@
       <c r="J40" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K40" s="31"/>
+      <c r="K40" s="23"/>
       <c r="L40" s="16">
         <v>46065</v>
       </c>
@@ -3419,7 +3230,7 @@
       <c r="J41" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K41" s="31"/>
+      <c r="K41" s="23"/>
       <c r="L41" s="16">
         <v>46065</v>
       </c>
@@ -3460,7 +3271,7 @@
       <c r="J42" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K42" s="31"/>
+      <c r="K42" s="23"/>
       <c r="L42" s="16">
         <v>46065</v>
       </c>
@@ -3501,7 +3312,7 @@
       <c r="J43" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K43" s="31"/>
+      <c r="K43" s="23"/>
       <c r="L43" s="16">
         <v>46065</v>
       </c>
@@ -3542,7 +3353,7 @@
       <c r="J44" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K44" s="31"/>
+      <c r="K44" s="23"/>
       <c r="L44" s="16">
         <v>46065</v>
       </c>
@@ -3583,7 +3394,7 @@
       <c r="J45" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K45" s="31"/>
+      <c r="K45" s="23"/>
       <c r="L45" s="16">
         <v>46065</v>
       </c>
@@ -3624,7 +3435,7 @@
       <c r="J46" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K46" s="31"/>
+      <c r="K46" s="23"/>
       <c r="L46" s="16">
         <v>46065</v>
       </c>
@@ -3665,7 +3476,7 @@
       <c r="J47" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K47" s="31"/>
+      <c r="K47" s="23"/>
       <c r="L47" s="16">
         <v>46065</v>
       </c>
@@ -3708,7 +3519,7 @@
       <c r="J48" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K48" s="31"/>
+      <c r="K48" s="23"/>
       <c r="L48" s="16">
         <v>46065</v>
       </c>
@@ -3749,7 +3560,7 @@
       <c r="J49" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K49" s="31"/>
+      <c r="K49" s="23"/>
       <c r="L49" s="16">
         <v>46065</v>
       </c>
@@ -3790,7 +3601,7 @@
       <c r="J50" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K50" s="31"/>
+      <c r="K50" s="23"/>
       <c r="L50" s="16">
         <v>46065</v>
       </c>
@@ -3831,7 +3642,7 @@
       <c r="J51" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K51" s="31"/>
+      <c r="K51" s="23"/>
       <c r="L51" s="16">
         <v>46065</v>
       </c>
@@ -3875,7 +3686,7 @@
       <c r="J52" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K52" s="31"/>
+      <c r="K52" s="23"/>
       <c r="L52" s="16">
         <v>46065</v>
       </c>
@@ -3916,7 +3727,7 @@
       <c r="J53" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K53" s="31"/>
+      <c r="K53" s="23"/>
       <c r="L53" s="16">
         <v>46044.375</v>
       </c>
@@ -3957,7 +3768,7 @@
       <c r="J54" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K54" s="31"/>
+      <c r="K54" s="23"/>
       <c r="L54" s="16">
         <v>46058.375</v>
       </c>
@@ -4001,7 +3812,7 @@
       <c r="J55" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K55" s="31"/>
+      <c r="K55" s="23"/>
       <c r="L55" s="16">
         <v>46048.375</v>
       </c>
@@ -4045,7 +3856,7 @@
       <c r="J56" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K56" s="31"/>
+      <c r="K56" s="23"/>
       <c r="L56" s="16">
         <v>46065</v>
       </c>
@@ -4089,7 +3900,7 @@
       <c r="J57" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K57" s="31"/>
+      <c r="K57" s="23"/>
       <c r="L57" s="16">
         <v>46065</v>
       </c>
@@ -4133,7 +3944,7 @@
       <c r="J58" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K58" s="31"/>
+      <c r="K58" s="23"/>
       <c r="L58" s="16">
         <v>46066</v>
       </c>
@@ -4174,7 +3985,7 @@
       <c r="J59" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="K59" s="31"/>
+      <c r="K59" s="23"/>
       <c r="L59" s="16">
         <v>46066</v>
       </c>
@@ -4215,7 +4026,7 @@
       <c r="J60" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="K60" s="31"/>
+      <c r="K60" s="23"/>
       <c r="L60" s="16">
         <v>46066</v>
       </c>
@@ -4259,7 +4070,7 @@
       <c r="J61" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="K61" s="31"/>
+      <c r="K61" s="23"/>
       <c r="L61" s="16">
         <v>46065</v>
       </c>
@@ -4300,7 +4111,7 @@
       <c r="J62" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="K62" s="31"/>
+      <c r="K62" s="23"/>
       <c r="L62" s="16">
         <v>46066</v>
       </c>
@@ -4341,7 +4152,7 @@
       <c r="J63" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="K63" s="31"/>
+      <c r="K63" s="23"/>
       <c r="L63" s="16">
         <v>46066</v>
       </c>
@@ -4385,7 +4196,7 @@
       <c r="J64" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="K64" s="31"/>
+      <c r="K64" s="23"/>
       <c r="L64" s="16">
         <v>46071</v>
       </c>
@@ -4429,7 +4240,7 @@
       <c r="J65" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="K65" s="31"/>
+      <c r="K65" s="23"/>
       <c r="L65" s="16">
         <v>46064</v>
       </c>
@@ -4470,7 +4281,7 @@
       <c r="J66" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="K66" s="31" t="s">
+      <c r="K66" s="23" t="s">
         <v>21</v>
       </c>
       <c r="L66" s="16">
@@ -4513,7 +4324,7 @@
       <c r="J67" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="K67" s="31" t="s">
+      <c r="K67" s="23" t="s">
         <v>21</v>
       </c>
       <c r="L67" s="16">
@@ -4556,7 +4367,7 @@
       <c r="J68" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="K68" s="31" t="s">
+      <c r="K68" s="23" t="s">
         <v>21</v>
       </c>
       <c r="L68" s="16">
@@ -4599,7 +4410,7 @@
       <c r="J69" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K69" s="31"/>
+      <c r="K69" s="23"/>
       <c r="L69" s="16">
         <v>46064</v>
       </c>
@@ -4643,7 +4454,7 @@
       <c r="J70" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K70" s="31"/>
+      <c r="K70" s="23"/>
       <c r="L70" s="16">
         <v>46064</v>
       </c>
@@ -4684,7 +4495,7 @@
       <c r="J71" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K71" s="31"/>
+      <c r="K71" s="23"/>
       <c r="L71" s="16">
         <v>46058.625</v>
       </c>
@@ -4728,7 +4539,7 @@
       <c r="J72" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K72" s="31"/>
+      <c r="K72" s="23"/>
       <c r="L72" s="16">
         <v>46058</v>
       </c>
@@ -4772,7 +4583,7 @@
       <c r="J73" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K73" s="31"/>
+      <c r="K73" s="23"/>
       <c r="L73" s="16">
         <v>46063</v>
       </c>
@@ -4813,7 +4624,7 @@
       <c r="J74" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K74" s="31"/>
+      <c r="K74" s="23"/>
       <c r="L74" s="16">
         <v>46058</v>
       </c>
@@ -4857,7 +4668,7 @@
       <c r="J75" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K75" s="31"/>
+      <c r="K75" s="23"/>
       <c r="L75" s="16">
         <v>46063</v>
       </c>
@@ -4898,7 +4709,7 @@
       <c r="J76" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K76" s="31"/>
+      <c r="K76" s="23"/>
       <c r="L76" s="16">
         <v>45699</v>
       </c>
@@ -4939,7 +4750,7 @@
       <c r="J77" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K77" s="31"/>
+      <c r="K77" s="23"/>
       <c r="L77" s="16">
         <v>46064</v>
       </c>
@@ -4980,7 +4791,7 @@
       <c r="J78" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K78" s="31"/>
+      <c r="K78" s="23"/>
       <c r="L78" s="16">
         <v>46064</v>
       </c>
@@ -5023,7 +4834,7 @@
       <c r="J79" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K79" s="31"/>
+      <c r="K79" s="23"/>
       <c r="L79" s="16">
         <v>46064</v>
       </c>
@@ -5064,7 +4875,7 @@
       <c r="J80" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K80" s="31"/>
+      <c r="K80" s="23"/>
       <c r="L80" s="16">
         <v>46064</v>
       </c>
@@ -5105,7 +4916,7 @@
       <c r="J81" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="K81" s="31"/>
+      <c r="K81" s="23"/>
       <c r="L81" s="16" t="s">
         <v>132</v>
       </c>
@@ -5146,7 +4957,7 @@
       <c r="J82" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="K82" s="31"/>
+      <c r="K82" s="23"/>
       <c r="L82" s="16" t="s">
         <v>132</v>
       </c>
@@ -5187,7 +4998,7 @@
       <c r="J83" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="K83" s="31" t="s">
+      <c r="K83" s="23" t="s">
         <v>21</v>
       </c>
       <c r="L83" s="16" t="s">
@@ -5230,7 +5041,7 @@
       <c r="J84" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="K84" s="31" t="s">
+      <c r="K84" s="23" t="s">
         <v>21</v>
       </c>
       <c r="L84" s="16" t="s">
@@ -5273,7 +5084,7 @@
       <c r="J85" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="K85" s="31"/>
+      <c r="K85" s="23"/>
       <c r="L85" s="16">
         <v>46071</v>
       </c>
@@ -5314,7 +5125,7 @@
       <c r="J86" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="K86" s="31"/>
+      <c r="K86" s="23"/>
       <c r="L86" s="16">
         <v>46071</v>
       </c>
@@ -5355,7 +5166,7 @@
       <c r="J87" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K87" s="31"/>
+      <c r="K87" s="23"/>
       <c r="L87" s="16">
         <v>46071</v>
       </c>
@@ -5399,7 +5210,7 @@
       <c r="J88" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="K88" s="31"/>
+      <c r="K88" s="23"/>
       <c r="L88" s="16">
         <v>46071</v>
       </c>
@@ -5440,7 +5251,7 @@
       <c r="J89" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="K89" s="31"/>
+      <c r="K89" s="23"/>
       <c r="L89" s="16">
         <v>46072</v>
       </c>
@@ -5481,7 +5292,7 @@
       <c r="J90" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K90" s="31"/>
+      <c r="K90" s="23"/>
       <c r="L90" s="16">
         <v>46073</v>
       </c>
@@ -5522,7 +5333,7 @@
       <c r="J91" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="K91" s="31"/>
+      <c r="K91" s="23"/>
       <c r="L91" s="16">
         <v>46073</v>
       </c>
@@ -5563,7 +5374,7 @@
       <c r="J92" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="K92" s="31"/>
+      <c r="K92" s="23"/>
       <c r="L92" s="16">
         <v>46072</v>
       </c>
@@ -5604,7 +5415,7 @@
       <c r="J93" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K93" s="31"/>
+      <c r="K93" s="23"/>
       <c r="L93" s="16">
         <v>46063</v>
       </c>
@@ -5645,7 +5456,7 @@
       <c r="J94" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K94" s="31"/>
+      <c r="K94" s="23"/>
       <c r="L94" s="16">
         <v>46063</v>
       </c>
@@ -5686,7 +5497,7 @@
       <c r="J95" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="K95" s="31"/>
+      <c r="K95" s="23"/>
       <c r="L95" s="16">
         <v>46072</v>
       </c>
@@ -5727,7 +5538,7 @@
       <c r="J96" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="K96" s="31"/>
+      <c r="K96" s="23"/>
       <c r="L96" s="16">
         <v>46072</v>
       </c>
@@ -5768,7 +5579,7 @@
       <c r="J97" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="K97" s="31"/>
+      <c r="K97" s="23"/>
       <c r="L97" s="16">
         <v>46063</v>
       </c>
@@ -5894,838 +5705,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2533B560-4010-4766-88F2-2CBCF406440B}">
-  <dimension ref="A1:G52"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" customWidth="1"/>
-    <col min="4" max="4" width="24.85546875" customWidth="1"/>
-    <col min="5" max="5" width="131.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="91.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="24" x14ac:dyDescent="0.4">
-      <c r="A1" s="32" t="s">
-        <v>158</v>
-      </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
-        <v>159</v>
-      </c>
-      <c r="B2" s="26" t="s">
-        <v>160</v>
-      </c>
-      <c r="C2" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="D2" s="26" t="s">
-        <v>162</v>
-      </c>
-      <c r="E2" s="26" t="s">
-        <v>163</v>
-      </c>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="27" t="s">
-        <v>164</v>
-      </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="27" t="s">
-        <v>165</v>
-      </c>
-      <c r="B4" s="27"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="27"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="27" t="s">
-        <v>166</v>
-      </c>
-      <c r="B5" s="27"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="27"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="27" t="s">
-        <v>167</v>
-      </c>
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="28"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="27"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="27"/>
-      <c r="B7" s="27"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="27"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="27"/>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="27"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="27"/>
-      <c r="B9" s="27"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="27"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="27"/>
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="28"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="27"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="27"/>
-      <c r="B11" s="27"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="27"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="27"/>
-      <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="27"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="27"/>
-      <c r="B13" s="27"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="27"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="27"/>
-      <c r="B14" s="27"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="28"/>
-      <c r="G14" s="27"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="27"/>
-      <c r="B15" s="27"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="27"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="27"/>
-      <c r="B16" s="27"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
-      <c r="G16" s="27"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="27"/>
-      <c r="B17" s="27"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="27"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="27"/>
-      <c r="B18" s="27"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="27"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="27"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="27"/>
-      <c r="B19" s="27"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="27"/>
-      <c r="B20" s="27"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="27"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="27"/>
-      <c r="B21" s="27"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="27"/>
-      <c r="F21" s="27"/>
-      <c r="G21" s="27"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="27"/>
-      <c r="B22" s="27"/>
-      <c r="C22" s="27"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="27"/>
-      <c r="F22" s="27"/>
-      <c r="G22" s="27"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="27"/>
-      <c r="B23" s="27"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="27"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="27"/>
-      <c r="B24" s="27"/>
-      <c r="C24" s="27"/>
-      <c r="D24" s="27"/>
-      <c r="E24" s="27"/>
-      <c r="F24" s="27"/>
-      <c r="G24" s="27"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="27"/>
-      <c r="B25" s="27"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="27"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="27"/>
-      <c r="B26" s="27"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="27"/>
-      <c r="E26" s="27"/>
-      <c r="F26" s="27"/>
-      <c r="G26" s="27"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="27"/>
-      <c r="B27" s="27"/>
-      <c r="C27" s="27"/>
-      <c r="D27" s="27"/>
-      <c r="E27" s="27"/>
-      <c r="F27" s="27"/>
-      <c r="G27" s="27"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="27"/>
-      <c r="B28" s="27"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="27"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="27"/>
-      <c r="B29" s="27"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="27"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="27"/>
-      <c r="B30" s="27"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="27"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="27"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="27"/>
-      <c r="B31" s="27"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="27"/>
-      <c r="E31" s="27"/>
-      <c r="F31" s="27"/>
-      <c r="G31" s="27"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="27"/>
-      <c r="B32" s="27"/>
-      <c r="C32" s="27"/>
-      <c r="D32" s="27"/>
-      <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="27"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="27"/>
-      <c r="B33" s="27"/>
-      <c r="C33" s="27"/>
-      <c r="D33" s="27"/>
-      <c r="E33" s="27"/>
-      <c r="F33" s="27"/>
-      <c r="G33" s="27"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="27"/>
-      <c r="B34" s="27"/>
-      <c r="C34" s="27"/>
-      <c r="D34" s="27"/>
-      <c r="E34" s="27"/>
-      <c r="F34" s="27"/>
-      <c r="G34" s="27"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="27"/>
-      <c r="B35" s="27"/>
-      <c r="C35" s="27"/>
-      <c r="D35" s="27"/>
-      <c r="E35" s="27"/>
-      <c r="F35" s="27"/>
-      <c r="G35" s="27"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="27"/>
-      <c r="B36" s="27"/>
-      <c r="C36" s="27"/>
-      <c r="D36" s="27"/>
-      <c r="E36" s="27"/>
-      <c r="F36" s="27"/>
-      <c r="G36" s="27"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="27"/>
-      <c r="B37" s="27"/>
-      <c r="C37" s="27"/>
-      <c r="D37" s="27"/>
-      <c r="E37" s="27"/>
-      <c r="F37" s="27"/>
-      <c r="G37" s="27"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="27"/>
-      <c r="B38" s="27"/>
-      <c r="C38" s="27"/>
-      <c r="D38" s="27"/>
-      <c r="E38" s="27"/>
-      <c r="F38" s="27"/>
-      <c r="G38" s="27"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="27"/>
-      <c r="B39" s="27"/>
-      <c r="C39" s="27"/>
-      <c r="D39" s="27"/>
-      <c r="E39" s="27"/>
-      <c r="F39" s="27"/>
-      <c r="G39" s="27"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="27"/>
-      <c r="B40" s="27"/>
-      <c r="C40" s="27"/>
-      <c r="D40" s="27"/>
-      <c r="E40" s="27"/>
-      <c r="F40" s="27"/>
-      <c r="G40" s="27"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="27"/>
-      <c r="B41" s="27"/>
-      <c r="C41" s="27"/>
-      <c r="D41" s="27"/>
-      <c r="E41" s="27"/>
-      <c r="F41" s="27"/>
-      <c r="G41" s="27"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="27"/>
-      <c r="B42" s="27"/>
-      <c r="C42" s="27"/>
-      <c r="D42" s="27"/>
-      <c r="E42" s="27"/>
-      <c r="F42" s="27"/>
-      <c r="G42" s="27"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="27"/>
-      <c r="B43" s="27"/>
-      <c r="C43" s="27"/>
-      <c r="D43" s="27"/>
-      <c r="E43" s="27"/>
-      <c r="F43" s="27"/>
-      <c r="G43" s="27"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="27"/>
-      <c r="B44" s="27"/>
-      <c r="C44" s="27"/>
-      <c r="D44" s="27"/>
-      <c r="E44" s="27"/>
-      <c r="F44" s="27"/>
-      <c r="G44" s="27"/>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="27"/>
-      <c r="B45" s="27"/>
-      <c r="C45" s="27"/>
-      <c r="D45" s="27"/>
-      <c r="E45" s="27"/>
-      <c r="F45" s="27"/>
-      <c r="G45" s="27"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="27"/>
-      <c r="B46" s="27"/>
-      <c r="C46" s="27"/>
-      <c r="D46" s="27"/>
-      <c r="E46" s="27"/>
-      <c r="F46" s="27"/>
-      <c r="G46" s="27"/>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="27"/>
-      <c r="B47" s="27"/>
-      <c r="C47" s="27"/>
-      <c r="D47" s="27"/>
-      <c r="E47" s="29"/>
-      <c r="F47" s="27"/>
-      <c r="G47" s="27"/>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="27"/>
-      <c r="B48" s="27"/>
-      <c r="C48" s="27"/>
-      <c r="D48" s="27"/>
-      <c r="E48" s="27"/>
-      <c r="F48" s="27"/>
-      <c r="G48" s="27"/>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="27"/>
-      <c r="B49" s="27"/>
-      <c r="C49" s="27"/>
-      <c r="D49" s="27"/>
-      <c r="E49" s="27"/>
-      <c r="F49" s="27"/>
-      <c r="G49" s="27"/>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="27"/>
-      <c r="B50" s="27"/>
-      <c r="C50" s="27"/>
-      <c r="D50" s="27"/>
-      <c r="E50" s="27"/>
-      <c r="F50" s="30"/>
-      <c r="G50" s="27"/>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="27"/>
-      <c r="B51" s="27"/>
-      <c r="C51" s="27"/>
-      <c r="D51" s="27"/>
-      <c r="E51" s="27"/>
-      <c r="F51" s="30"/>
-      <c r="G51" s="27"/>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="27"/>
-      <c r="B52" s="27"/>
-      <c r="C52" s="27"/>
-      <c r="D52" s="27"/>
-      <c r="E52" s="27"/>
-      <c r="F52" s="27"/>
-      <c r="G52" s="27"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B0D0267-C0B1-4666-B8FC-FDA077DFCAF0}">
-  <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="10.85546875" customWidth="1"/>
-    <col min="2" max="2" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.28515625" customWidth="1"/>
-    <col min="4" max="4" width="27.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="48.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" s="24" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
-        <v>168</v>
-      </c>
-      <c r="B1" s="23" t="s">
-        <v>169</v>
-      </c>
-      <c r="C1" s="23" t="s">
-        <v>170</v>
-      </c>
-      <c r="D1" s="23" t="s">
-        <v>171</v>
-      </c>
-      <c r="E1" s="23" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>173</v>
-      </c>
-      <c r="B2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E2" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>173</v>
-      </c>
-      <c r="B3" t="s">
-        <v>175</v>
-      </c>
-      <c r="C3" t="s">
-        <v>175</v>
-      </c>
-      <c r="D3" t="s">
-        <v>176</v>
-      </c>
-      <c r="E3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B4" t="s">
-        <v>178</v>
-      </c>
-      <c r="C4" t="s">
-        <v>178</v>
-      </c>
-      <c r="D4" t="s">
-        <v>83</v>
-      </c>
-      <c r="E4" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>173</v>
-      </c>
-      <c r="B5" t="s">
-        <v>180</v>
-      </c>
-      <c r="C5" t="s">
-        <v>180</v>
-      </c>
-      <c r="D5" t="s">
-        <v>83</v>
-      </c>
-      <c r="E5" s="25" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>173</v>
-      </c>
-      <c r="B6" t="s">
-        <v>182</v>
-      </c>
-      <c r="C6" t="s">
-        <v>182</v>
-      </c>
-      <c r="D6" t="s">
-        <v>83</v>
-      </c>
-      <c r="E6" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>173</v>
-      </c>
-      <c r="B7" t="s">
-        <v>182</v>
-      </c>
-      <c r="C7" t="s">
-        <v>182</v>
-      </c>
-      <c r="D7" t="s">
-        <v>83</v>
-      </c>
-      <c r="E7" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>173</v>
-      </c>
-      <c r="B8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" t="s">
-        <v>69</v>
-      </c>
-      <c r="D8" t="s">
-        <v>83</v>
-      </c>
-      <c r="E8" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>173</v>
-      </c>
-      <c r="B9" t="s">
-        <v>186</v>
-      </c>
-      <c r="C9" t="s">
-        <v>186</v>
-      </c>
-      <c r="D9" t="s">
-        <v>68</v>
-      </c>
-      <c r="E9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>173</v>
-      </c>
-      <c r="B10" t="s">
-        <v>188</v>
-      </c>
-      <c r="C10" t="s">
-        <v>188</v>
-      </c>
-      <c r="D10" t="s">
-        <v>68</v>
-      </c>
-      <c r="E10" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>190</v>
-      </c>
-      <c r="B11" t="s">
-        <v>191</v>
-      </c>
-      <c r="C11" t="s">
-        <v>191</v>
-      </c>
-      <c r="D11" t="s">
-        <v>192</v>
-      </c>
-      <c r="E11" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>190</v>
-      </c>
-      <c r="B12" t="s">
-        <v>194</v>
-      </c>
-      <c r="C12" t="s">
-        <v>194</v>
-      </c>
-      <c r="D12" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>190</v>
-      </c>
-      <c r="B13" t="s">
-        <v>195</v>
-      </c>
-      <c r="C13" t="s">
-        <v>195</v>
-      </c>
-      <c r="D13" t="s">
-        <v>30</v>
-      </c>
-      <c r="E13" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>190</v>
-      </c>
-      <c r="B14" t="s">
-        <v>196</v>
-      </c>
-      <c r="C14" t="s">
-        <v>196</v>
-      </c>
-      <c r="D14" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>190</v>
-      </c>
-      <c r="B15" t="s">
-        <v>197</v>
-      </c>
-      <c r="C15" t="s">
-        <v>197</v>
-      </c>
-      <c r="D15" t="s">
-        <v>77</v>
-      </c>
-      <c r="E15" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>190</v>
-      </c>
-      <c r="B16" t="s">
-        <v>198</v>
-      </c>
-      <c r="C16" t="s">
-        <v>198</v>
-      </c>
-      <c r="D16" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>190</v>
-      </c>
-      <c r="B17" t="s">
-        <v>199</v>
-      </c>
-      <c r="C17" t="s">
-        <v>199</v>
-      </c>
-      <c r="D17" t="s">
-        <v>44</v>
-      </c>
-      <c r="E17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-</worksheet>
-</file>
-
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c07156c6-b3d6-47fe-90fe-41d94611589a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100D7C5257DA587DC41A66EC59D887286DA" ma:contentTypeVersion="13" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="c1ca4ba6d79ccd11599f74f585a5944d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c07156c6-b3d6-47fe-90fe-41d94611589a" xmlns:ns3="b6a5a379-3ccd-47e7-92d4-dee7b1a3a097" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a555085ee284c9966e73d8d59c393e3c" ns2:_="" ns3:_="">
     <xsd:import namespace="c07156c6-b3d6-47fe-90fe-41d94611589a"/>
@@ -6942,10 +5922,40 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c07156c6-b3d6-47fe-90fe-41d94611589a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E1D50D8-1F6C-4041-A785-B1C5CBC22D2A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D672392-DCAE-426E-84C4-27BD71761413}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="c07156c6-b3d6-47fe-90fe-41d94611589a"/>
+    <ds:schemaRef ds:uri="b6a5a379-3ccd-47e7-92d4-dee7b1a3a097"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6968,20 +5978,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D672392-DCAE-426E-84C4-27BD71761413}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E1D50D8-1F6C-4041-A785-B1C5CBC22D2A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="c07156c6-b3d6-47fe-90fe-41d94611589a"/>
-    <ds:schemaRef ds:uri="b6a5a379-3ccd-47e7-92d4-dee7b1a3a097"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>